--- a/informes_data/Primera FEB/2025-26/playoffs/individual/NP_play_by_play_2513264_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/playoffs/individual/NP_play_by_play_2513264_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.7503</v>
+        <v>6.8984</v>
       </c>
       <c r="E2" t="n">
-        <v>6.9921</v>
+        <v>7.8231</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.2418</v>
+        <v>-0.9247</v>
       </c>
       <c r="G2" t="n">
         <v>6.1181</v>
@@ -610,13 +610,13 @@
         <v>1.3216</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.4867</v>
+        <v>-0.3386</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7687</v>
+        <v>0.0624</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.7181</v>
+        <v>-0.401</v>
       </c>
       <c r="V2" t="n">
         <v>1.1189</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.1416</v>
+        <v>4.7044</v>
       </c>
       <c r="E3" t="n">
-        <v>5.6072</v>
+        <v>4.9683</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4656</v>
+        <v>-0.2639</v>
       </c>
       <c r="G3" t="n">
         <v>2.7317</v>
@@ -688,13 +688,13 @@
         <v>1.9825</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7234</v>
+        <v>0.2863</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5105</v>
+        <v>0.8716</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.7871</v>
+        <v>-0.5853</v>
       </c>
       <c r="V3" t="n">
         <v>-0.07580000000000001</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8678</v>
+        <v>2.0866</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3476</v>
+        <v>0.8259</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5201</v>
+        <v>1.2607</v>
       </c>
       <c r="G4" t="n">
         <v>0.9727</v>
@@ -766,13 +766,13 @@
         <v>1.5419</v>
       </c>
       <c r="S4" t="n">
-        <v>1.5611</v>
+        <v>0.7799</v>
       </c>
       <c r="T4" t="n">
-        <v>1.7027</v>
+        <v>1.1809</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1416</v>
+        <v>-0.401</v>
       </c>
       <c r="V4" t="n">
         <v>0.1137</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. DIAZ</t>
+          <t>D. MANCHON CRESPO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,40 +799,40 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1258</v>
+        <v>2.0511</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8389</v>
+        <v>0.2041</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.7131</v>
+        <v>1.847</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8692</v>
+        <v>1.4407</v>
       </c>
       <c r="H5" t="n">
-        <v>1.7599</v>
+        <v>2.1871</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8907</v>
+        <v>-0.7465000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5062</v>
+        <v>-0.0505</v>
       </c>
       <c r="K5" t="n">
-        <v>1.8152</v>
+        <v>0.8282</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.3091</v>
+        <v>-0.8787</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.637</v>
+        <v>1.4911</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0554</v>
+        <v>1.3589</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5816</v>
+        <v>0.1322</v>
       </c>
       <c r="P5" t="n">
         <v>0.8811</v>
@@ -844,28 +844,28 @@
         <v>0.8811</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3637</v>
+        <v>-0.2706</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3327</v>
+        <v>0.2546</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6964</v>
+        <v>-0.5252</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2608</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2608</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. MANCHON CRESPO</t>
+          <t>M. DIAZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,40 +877,40 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0119</v>
+        <v>1.6567</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6909999999999999</v>
+        <v>2.2544</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7029</v>
+        <v>-0.5978</v>
       </c>
       <c r="G6" t="n">
-        <v>1.4407</v>
+        <v>0.8692</v>
       </c>
       <c r="H6" t="n">
-        <v>2.1871</v>
+        <v>1.7599</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7465000000000001</v>
+        <v>-0.8907</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.0505</v>
+        <v>1.5062</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8282</v>
+        <v>1.8152</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.8787</v>
+        <v>-0.3091</v>
       </c>
       <c r="M6" t="n">
-        <v>1.4911</v>
+        <v>-0.637</v>
       </c>
       <c r="N6" t="n">
-        <v>1.3589</v>
+        <v>-0.0554</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1322</v>
+        <v>-0.5816</v>
       </c>
       <c r="P6" t="n">
         <v>0.8811</v>
@@ -922,28 +922,28 @@
         <v>0.8811</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.3099</v>
+        <v>0.1672</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6405999999999999</v>
+        <v>0.7482</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6693</v>
+        <v>-0.5810999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.2608</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.2608</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B. DE BISSCHOP</t>
+          <t>B. VIDARTE CANO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1963</v>
+        <v>-0.1398</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.5955</v>
+        <v>-0.1281</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3993</v>
+        <v>-0.0117</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1335</v>
+        <v>-0.0673</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0746</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2081</v>
+        <v>-0.0673</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1913</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6441</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8354</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0578</v>
+        <v>-0.0673</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5695</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6273</v>
+        <v>-0.0673</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.8811</v>
+        <v>0.2203</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.423</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5419</v>
+        <v>0.2203</v>
       </c>
       <c r="S7" t="n">
-        <v>1.8597</v>
+        <v>-0.032</v>
       </c>
       <c r="T7" t="n">
-        <v>1.5746</v>
+        <v>-0.1281</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2851</v>
+        <v>0.0961</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.3084</v>
+        <v>-0.2608</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.9384</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.37</v>
+        <v>-0.2608</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B. VIDARTE CANO</t>
+          <t>B. DE BISSCHOP</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1975</v>
+        <v>-1.1811</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1281</v>
+        <v>-2.2344</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0694</v>
+        <v>1.0534</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0673</v>
+        <v>0.1335</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>-0.0746</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0673</v>
+        <v>0.2081</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>0.1913</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>-0.6441</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.8354</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0673</v>
+        <v>-0.0578</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>0.5695</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0673</v>
+        <v>-0.6273</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2203</v>
+        <v>-0.8811</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.423</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2203</v>
+        <v>1.5419</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0897</v>
+        <v>0.8749</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1281</v>
+        <v>0.9357</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0384</v>
+        <v>-0.0608</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2608</v>
+        <v>-1.3084</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.9384</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2608</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0862</v>
+        <v>-2.5476</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8951</v>
+        <v>-1.5871</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1911</v>
+        <v>-0.9605</v>
       </c>
       <c r="G9" t="n">
         <v>-0.8772</v>
@@ -1156,13 +1156,13 @@
         <v>0.4405</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7427</v>
+        <v>0.2812</v>
       </c>
       <c r="T9" t="n">
-        <v>1.0497</v>
+        <v>0.3577</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3071</v>
+        <v>-0.0765</v>
       </c>
       <c r="V9" t="n">
         <v>-0.1895</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. BELEMENE-DZABATOU</t>
+          <t>V. ALVES BENITE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.4009</v>
+        <v>-3.2086</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1818</v>
+        <v>-2.8139</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.2191</v>
+        <v>-0.3947</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.6653</v>
+        <v>-2.8981</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1451</v>
+        <v>-1.5138</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8104</v>
+        <v>-1.3843</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3491</v>
+        <v>-0.8579</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0359</v>
+        <v>-1.5525</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.385</v>
+        <v>0.6946</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.3162</v>
+        <v>-2.0402</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1092</v>
+        <v>0.0387</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4254</v>
+        <v>-2.0789</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.2203</v>
+        <v>-1.1014</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1014</v>
+        <v>-2.423</v>
       </c>
       <c r="R10" t="n">
-        <v>0.8811</v>
+        <v>1.3216</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0167</v>
+        <v>0.7909</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2686</v>
+        <v>0.467</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2854</v>
+        <v>0.3239</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.4986</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.4986</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>V. ALVES BENITE</t>
+          <t>J. BELEMENE-DZABATOU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.0183</v>
+        <v>-3.3611</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.1136</v>
+        <v>-1.1708</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0953</v>
+        <v>-2.1903</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.8981</v>
+        <v>-0.6653</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.5138</v>
+        <v>0.1451</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.3843</v>
+        <v>-0.8104</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.8579</v>
+        <v>-0.3491</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.5525</v>
+        <v>0.0359</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6946</v>
+        <v>-0.385</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.0402</v>
+        <v>-0.3162</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0387</v>
+        <v>0.1092</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.0789</v>
+        <v>-0.4254</v>
       </c>
       <c r="P11" t="n">
+        <v>-0.2203</v>
+      </c>
+      <c r="Q11" t="n">
         <v>-1.1014</v>
       </c>
-      <c r="Q11" t="n">
-        <v>-2.423</v>
-      </c>
       <c r="R11" t="n">
-        <v>1.3216</v>
+        <v>0.8811</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0188</v>
+        <v>0.023</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8327</v>
+        <v>0.2796</v>
       </c>
       <c r="U11" t="n">
-        <v>0.8139</v>
+        <v>-0.2565</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-2.4986</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-2.4986</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.998200000000001</v>
+        <v>6.958999999999996</v>
       </c>
       <c r="E12" t="n">
-        <v>7.1807</v>
+        <v>8.141499999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.1825</v>
+        <v>-1.182500000000001</v>
       </c>
       <c r="G12" t="n">
         <v>7.758000000000001</v>
@@ -1366,7 +1366,7 @@
         <v>11.5264</v>
       </c>
       <c r="K12" t="n">
-        <v>7.272500000000001</v>
+        <v>7.272499999999999</v>
       </c>
       <c r="L12" t="n">
         <v>4.2539</v>
@@ -1381,7 +1381,7 @@
         <v>-7.162</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>-5.551115123125783e-17</v>
       </c>
       <c r="Q12" t="n">
         <v>-11.0136</v>
@@ -1390,13 +1390,13 @@
         <v>11.0136</v>
       </c>
       <c r="S12" t="n">
-        <v>1.6014</v>
+        <v>2.5622</v>
       </c>
       <c r="T12" t="n">
-        <v>4.068700000000001</v>
+        <v>5.029599999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.4676</v>
+        <v>-2.4674</v>
       </c>
       <c r="V12" t="n">
         <v>-3.3613</v>
@@ -1405,7 +1405,7 @@
         <v>2.5988</v>
       </c>
       <c r="X12" t="n">
-        <v>-5.9602</v>
+        <v>-5.960199999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.9021</v>
+        <v>2.0788</v>
       </c>
       <c r="E13" t="n">
-        <v>1.1927</v>
+        <v>1.427</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7094</v>
+        <v>0.6518</v>
       </c>
       <c r="G13" t="n">
         <v>1.7203</v>
@@ -1468,13 +1468,13 @@
         <v>0.4405</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2587</v>
+        <v>-0.082</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5124</v>
+        <v>-0.2781</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2537</v>
+        <v>0.1961</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>I. JAKOVICS</t>
+          <t>A. KUNKEL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.2573</v>
+        <v>1.771</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3581</v>
+        <v>1.783</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8992</v>
+        <v>-0.0121</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.5316</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.7032</v>
+        <v>0.3373</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1716</v>
+        <v>-0.3461</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.6287</v>
+        <v>0.4955</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.4446</v>
+        <v>0.7286</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.1841</v>
+        <v>-0.2331</v>
       </c>
       <c r="M14" t="n">
-        <v>0.09710000000000001</v>
+        <v>-0.5043</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2586</v>
+        <v>-0.3913</v>
       </c>
       <c r="O14" t="n">
-        <v>0.3557</v>
+        <v>-0.113</v>
       </c>
       <c r="P14" t="n">
-        <v>0.4405</v>
+        <v>0.8811</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1014</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5419</v>
+        <v>0.8811</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.07439999999999999</v>
+        <v>-0.2203</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6654</v>
+        <v>0.1686</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7398</v>
+        <v>-0.3889</v>
       </c>
       <c r="V14" t="n">
-        <v>2.4228</v>
+        <v>1.1189</v>
       </c>
       <c r="W14" t="n">
-        <v>2.4228</v>
+        <v>1.1189</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. MUNOZ BORCHERS</t>
+          <t>I. JAKOVICS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1634</v>
+        <v>1.2536</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1935</v>
+        <v>0.1238</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9699</v>
+        <v>1.1298</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.3024</v>
+        <v>-1.5316</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.5055</v>
+        <v>-1.7032</v>
       </c>
       <c r="I15" t="n">
-        <v>1.2031</v>
+        <v>0.1716</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.1392</v>
+        <v>-1.6287</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.5442</v>
+        <v>-1.4446</v>
       </c>
       <c r="L15" t="n">
-        <v>1.405</v>
+        <v>-0.1841</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1632</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0387</v>
+        <v>-0.2586</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.2019</v>
+        <v>0.3557</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1014</v>
+        <v>0.4405</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.1014</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1014</v>
+        <v>1.5419</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5494</v>
+        <v>-0.0781</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3327</v>
+        <v>0.4311</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2167</v>
+        <v>-0.5092</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.185</v>
+        <v>2.4228</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.4228</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.185</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. KUNKEL</t>
+          <t>A. MUNOZ BORCHERS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8336</v>
+        <v>0.9002</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8457</v>
+        <v>-0.0408</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0121</v>
+        <v>0.9411</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.3024</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3373</v>
+        <v>-1.5055</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3461</v>
+        <v>1.2031</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4955</v>
+        <v>-0.1392</v>
       </c>
       <c r="K16" t="n">
-        <v>0.7286</v>
+        <v>-1.5442</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.2331</v>
+        <v>1.405</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.5043</v>
+        <v>-0.1632</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3913</v>
+        <v>0.0387</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.113</v>
+        <v>-0.2019</v>
       </c>
       <c r="P16" t="n">
-        <v>0.8811</v>
+        <v>1.1014</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.8811</v>
+        <v>1.1014</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1576</v>
+        <v>0.2863</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7687</v>
+        <v>0.0984</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3889</v>
+        <v>0.1879</v>
       </c>
       <c r="V16" t="n">
-        <v>1.1189</v>
+        <v>-0.185</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1189</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.185</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4717</v>
+        <v>-0.3257</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0357</v>
+        <v>0.0814</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.436</v>
+        <v>-0.4071</v>
       </c>
       <c r="G17" t="n">
         <v>-1.1511</v>
@@ -1780,13 +1780,13 @@
         <v>1.7622</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2035</v>
+        <v>0.3495</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0516</v>
+        <v>0.0655</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2552</v>
+        <v>0.284</v>
       </c>
       <c r="V17" t="n">
         <v>-0.185</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. KAMBA</t>
+          <t>A. WINTERING</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6145</v>
+        <v>-1.7376</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8948</v>
+        <v>0.8253</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.5093</v>
+        <v>-2.5628</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.05</v>
+        <v>0.4066</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0581</v>
+        <v>-2.3308</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.9919</v>
+        <v>2.7374</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4216</v>
+        <v>3.7514</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6927</v>
+        <v>-0.5722</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.2711</v>
+        <v>4.3236</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.4716</v>
+        <v>-3.3448</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7508</v>
+        <v>-1.7586</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.7208</v>
+        <v>-1.5862</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2203</v>
+        <v>-2.2027</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1014</v>
+        <v>-3.3041</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3216</v>
+        <v>1.1014</v>
       </c>
       <c r="S18" t="n">
-        <v>1.2152</v>
+        <v>-0.1309</v>
       </c>
       <c r="T18" t="n">
-        <v>1.5746</v>
+        <v>0.378</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3594</v>
+        <v>-0.5088</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.1895</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.1895</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. WINTERING</t>
+          <t>M. KAMBA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3572</v>
+        <v>-1.7536</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1768</v>
+        <v>-0.0425</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.534</v>
+        <v>-1.7111</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4066</v>
+        <v>-2.05</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.3308</v>
+        <v>-0.0581</v>
       </c>
       <c r="I19" t="n">
-        <v>2.7374</v>
+        <v>-1.9919</v>
       </c>
       <c r="J19" t="n">
-        <v>3.7514</v>
+        <v>0.4216</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5722</v>
+        <v>0.6927</v>
       </c>
       <c r="L19" t="n">
-        <v>4.3236</v>
+        <v>-0.2711</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.3448</v>
+        <v>-2.4716</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.7586</v>
+        <v>-0.7508</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.5862</v>
+        <v>-1.7208</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.2027</v>
+        <v>0.2203</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.3041</v>
+        <v>-1.1014</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1014</v>
+        <v>1.3216</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2494</v>
+        <v>0.0761</v>
       </c>
       <c r="T19" t="n">
-        <v>0.7294</v>
+        <v>0.6373</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.48</v>
+        <v>-0.5611</v>
       </c>
       <c r="V19" t="n">
-        <v>0.1895</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.1895</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. ARMUS</t>
+          <t>T. BORG</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.3142</v>
+        <v>-2.0358</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0837</v>
+        <v>-1.0499</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2305</v>
+        <v>-0.9859</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.7182</v>
+        <v>0.0546</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.8244</v>
+        <v>0.3041</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1062</v>
+        <v>-0.2495</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.5623</v>
+        <v>0.6059</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.7142</v>
+        <v>0.8986</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1519</v>
+        <v>-0.2927</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1559</v>
+        <v>-0.5513</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1102</v>
+        <v>-0.5946</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0457</v>
+        <v>0.0433</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4405</v>
+        <v>-0.8811</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.2027</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4405</v>
+        <v>1.3216</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.032</v>
+        <v>-0.6499</v>
       </c>
       <c r="T20" t="n">
-        <v>0.8576</v>
+        <v>-0.0126</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8895999999999999</v>
+        <v>-0.6373</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.0045</v>
+        <v>-0.5595</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.3789</v>
+        <v>0.5595</v>
       </c>
       <c r="X20" t="n">
-        <v>0.3745</v>
+        <v>-1.1189</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T. BORG</t>
+          <t>M. ARMUS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.8559</v>
+        <v>-2.927</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.8701</v>
+        <v>-1.5524</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9859</v>
+        <v>-1.3746</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0546</v>
+        <v>-2.7182</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3041</v>
+        <v>-2.8244</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2495</v>
+        <v>0.1062</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6059</v>
+        <v>-1.5623</v>
       </c>
       <c r="K21" t="n">
-        <v>0.8986</v>
+        <v>-1.7142</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.2927</v>
+        <v>0.1519</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.5513</v>
+        <v>-1.1559</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5946</v>
+        <v>-1.1102</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0433</v>
+        <v>-0.0457</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.8811</v>
+        <v>0.4405</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.2027</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3216</v>
+        <v>0.4405</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.47</v>
+        <v>-0.6448</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8327</v>
+        <v>0.3889</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6373</v>
+        <v>-1.0337</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.5595</v>
+        <v>-0.0045</v>
       </c>
       <c r="W21" t="n">
-        <v>0.5595</v>
+        <v>-0.3789</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.1189</v>
+        <v>0.3745</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.5412</v>
+        <v>-3.2222</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.4897</v>
+        <v>-0.3725</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.0515</v>
+        <v>-2.8497</v>
       </c>
       <c r="G22" t="n">
         <v>-2.1774</v>
@@ -2170,13 +2170,13 @@
         <v>1.1014</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8263</v>
+        <v>-0.5074</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4732</v>
+        <v>0.5904</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.2995</v>
+        <v>-1.0978</v>
       </c>
       <c r="V22" t="n">
         <v>0.5639</v>
@@ -2209,22 +2209,22 @@
         <v>1.1824</v>
       </c>
       <c r="F23" t="n">
-        <v>-7.1808</v>
+        <v>-7.1806</v>
       </c>
       <c r="G23" t="n">
-        <v>-7.758000000000001</v>
+        <v>-7.757999999999999</v>
       </c>
       <c r="H23" t="n">
         <v>-10.6659</v>
       </c>
       <c r="I23" t="n">
-        <v>2.907900000000001</v>
+        <v>2.9079</v>
       </c>
       <c r="J23" t="n">
-        <v>3.7685</v>
+        <v>3.768499999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.3934</v>
+        <v>-3.393400000000001</v>
       </c>
       <c r="L23" t="n">
         <v>7.162000000000001</v>
@@ -2236,7 +2236,7 @@
         <v>-7.2726</v>
       </c>
       <c r="O23" t="n">
-        <v>-4.2539</v>
+        <v>-4.253900000000001</v>
       </c>
       <c r="P23" t="n">
         <v>-9.999999999976694e-05</v>
@@ -2254,13 +2254,13 @@
         <v>2.4675</v>
       </c>
       <c r="U23" t="n">
-        <v>-4.0689</v>
+        <v>-4.0688</v>
       </c>
       <c r="V23" t="n">
         <v>3.3611</v>
       </c>
       <c r="W23" t="n">
-        <v>5.9601</v>
+        <v>5.960100000000001</v>
       </c>
       <c r="X23" t="n">
         <v>-2.5988</v>
